--- a/base_datos/Preguntas_Robot_EVA_EvaSIM.xlsx
+++ b/base_datos/Preguntas_Robot_EVA_EvaSIM.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O229"/>
+  <dimension ref="A1:O231"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" style="8" min="1" max="1"/>
@@ -981,7 +981,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -1050,7 +1049,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -1119,7 +1117,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -1188,7 +1185,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -1257,7 +1253,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -1326,7 +1321,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -1395,7 +1389,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -1464,7 +1457,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -1533,7 +1525,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -1602,7 +1593,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -1671,7 +1661,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -1740,7 +1729,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -1809,7 +1797,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -1878,7 +1865,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -1947,7 +1933,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -2016,7 +2001,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -2085,7 +2069,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -2150,7 +2133,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -2215,7 +2197,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -2280,7 +2261,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -2345,7 +2325,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -2410,7 +2389,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -2475,7 +2453,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -2540,7 +2517,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -2605,7 +2581,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -2670,7 +2645,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -2735,7 +2709,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -2800,7 +2773,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -2869,7 +2841,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -2938,7 +2909,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -3007,7 +2977,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -3072,7 +3041,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -3137,7 +3105,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -3206,7 +3173,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -3275,7 +3241,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -3344,7 +3309,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -3413,7 +3377,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -3482,7 +3445,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -3551,7 +3513,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -3620,7 +3581,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -3689,7 +3649,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -3758,7 +3717,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -3827,7 +3785,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -3896,7 +3853,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -3965,7 +3921,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -4034,7 +3989,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -4099,7 +4053,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -4164,7 +4117,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -4229,7 +4181,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -4294,7 +4245,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -4359,7 +4309,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -4424,7 +4373,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -4489,7 +4437,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -4554,7 +4501,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -4619,7 +4565,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -4684,7 +4629,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -4749,7 +4693,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -4814,7 +4757,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -4879,7 +4821,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -4944,7 +4885,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -5009,7 +4949,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -5074,7 +5013,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -5139,7 +5077,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -5204,7 +5141,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -5411,7 +5347,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -5476,7 +5411,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -5541,7 +5475,6 @@
           <t>Triste</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -5606,7 +5539,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -5673,7 +5605,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -5738,7 +5669,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -5803,7 +5733,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -5868,7 +5797,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -5933,7 +5861,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -5998,7 +5925,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -6063,7 +5989,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -6128,7 +6053,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -6193,7 +6117,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -6258,7 +6181,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -6323,7 +6245,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -6388,7 +6309,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -6453,7 +6373,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -6518,7 +6437,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -6583,7 +6501,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -6648,7 +6565,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -6713,7 +6629,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -6778,7 +6693,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -6843,7 +6757,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -6908,7 +6821,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -6973,7 +6885,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -7038,7 +6949,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -7103,7 +7013,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -7172,7 +7081,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -7241,7 +7149,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -7310,7 +7217,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -7379,7 +7285,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -7448,7 +7353,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -7517,7 +7421,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -7586,7 +7489,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -7655,7 +7557,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -7724,7 +7625,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -7793,7 +7693,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -7862,7 +7761,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -7931,7 +7829,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -8000,7 +7897,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -8069,7 +7965,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -8138,7 +8033,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -8207,7 +8101,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -8276,7 +8169,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -8345,7 +8237,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -8414,7 +8305,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -8483,7 +8373,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -8552,7 +8441,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -8621,7 +8509,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -8690,7 +8577,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -8759,7 +8645,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -8828,7 +8713,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -8897,7 +8781,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -8966,7 +8849,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -9035,7 +8917,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -9104,7 +8985,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -9173,7 +9053,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -9242,7 +9121,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -9311,7 +9189,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -9380,7 +9257,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -9449,7 +9325,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -9518,7 +9393,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -9587,7 +9461,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -9656,7 +9529,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -9725,7 +9597,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -9794,7 +9665,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -9863,7 +9733,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -9932,7 +9801,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -10001,7 +9869,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -10070,7 +9937,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -10139,7 +10005,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -10208,7 +10073,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -10277,7 +10141,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -10346,7 +10209,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -10415,7 +10277,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -10484,7 +10345,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -10553,7 +10413,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -10622,7 +10481,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -10691,7 +10549,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -10760,7 +10617,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -10829,7 +10685,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -10898,7 +10753,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -10967,7 +10821,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -11036,7 +10889,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -11105,7 +10957,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -11174,7 +11025,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -11243,7 +11093,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -11312,7 +11161,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -11381,7 +11229,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -11450,7 +11297,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -11519,7 +11365,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -11588,7 +11433,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -11657,7 +11501,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -11726,7 +11569,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -11795,7 +11637,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -11864,7 +11705,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -11933,7 +11773,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -12002,7 +11841,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -12071,7 +11909,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -12140,7 +11977,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -12209,7 +12045,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -12278,7 +12113,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -12347,7 +12181,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -12416,7 +12249,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -12485,7 +12317,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -12554,7 +12385,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -12623,7 +12453,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -12692,7 +12521,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -12761,7 +12589,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -12830,7 +12657,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -12899,7 +12725,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -12968,7 +12793,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -13037,7 +12861,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -13106,7 +12929,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -13175,7 +12997,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -13244,7 +13065,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -13313,7 +13133,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -13382,7 +13201,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -13451,7 +13269,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -13520,7 +13337,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -13589,7 +13405,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -13658,7 +13473,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -13727,7 +13541,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -13796,7 +13609,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -13865,7 +13677,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -13934,7 +13745,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -14003,7 +13813,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -14072,7 +13881,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -14141,7 +13949,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -14210,7 +14017,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -14279,7 +14085,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -14348,7 +14153,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -14417,7 +14221,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -14486,7 +14289,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -14555,7 +14357,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -14624,7 +14425,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -14693,7 +14493,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -14762,7 +14561,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -14831,7 +14629,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -14900,7 +14697,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -14969,7 +14765,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -15038,7 +14833,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -15107,7 +14901,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -15176,7 +14969,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -15245,7 +15037,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -15314,7 +15105,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -15383,7 +15173,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -15452,7 +15241,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -15521,7 +15309,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -15590,7 +15377,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -15659,7 +15445,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -15728,7 +15513,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -15797,7 +15581,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -15866,7 +15649,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -15935,7 +15717,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -16004,7 +15785,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -16073,7 +15853,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr">
         <is>
           <t>Derecha</t>
@@ -16142,7 +15921,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr">
         <is>
           <t>Girar 360°</t>
@@ -16211,7 +15989,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr">
         <is>
           <t>Adelante</t>
@@ -16280,7 +16057,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr">
         <is>
           <t>Atrás</t>
@@ -16349,7 +16125,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr">
         <is>
           <t>Izquierda</t>
@@ -16418,15 +16193,148 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
           <t>Derecha</t>
         </is>
       </c>
     </row>
-    <row r="230" s="8"/>
-    <row r="231" s="8"/>
+    <row r="230" s="8">
+      <c r="A230" t="n">
+        <v>247</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Interacción: música agregada a mano</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Interacción — Pregunta</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Te voy a poner una canción, ¿sabes cómo se llama?</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Danza Kuduro</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Feliz / Neutral / Triste</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Socialización / conversación</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Reconocimiento Musical</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Feliz</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Triste</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>danza-kuduro.mp3</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Atrás</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" s="8">
+      <c r="A231" t="n">
+        <v>248</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Interacción: música agregada a mano</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Interacción — Pregunta</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Escuchá esto, ¿qué canción es?</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>More Than Words</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Feliz / Neutral / Triste</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Socialización / conversación</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Reconocimiento Musical</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Feliz</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Triste</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>more-than-words-heaven.mp3</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Izquierda</t>
+        </is>
+      </c>
+    </row>
     <row r="232" s="8"/>
     <row r="233" s="8"/>
     <row r="234" s="8"/>

--- a/base_datos/Preguntas_Robot_EVA_EvaSIM.xlsx
+++ b/base_datos/Preguntas_Robot_EVA_EvaSIM.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O231"/>
+  <dimension ref="A1:O226"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" style="8" min="1" max="1"/>
@@ -6701,11 +6701,11 @@
     </row>
     <row r="90" s="8">
       <c r="A90" s="6" t="n">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Chistes</t>
+          <t>Preguntas y Respuestas</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
@@ -6713,15 +6713,19 @@
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Chiste</t>
+          <t>Pregunta de contenido</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la fruta más divertida?</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="n"/>
+          <t>El triángulo que tiene sus tres lados iguales ¿Cómo se llama?</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Equilátero</t>
+        </is>
+      </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
           <t>Neutral</t>
@@ -6729,7 +6733,7 @@
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>Chiste</t>
+          <t>Trivia / conocimiento</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
@@ -6739,7 +6743,7 @@
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>Chistes</t>
+          <t>Trivia</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
@@ -6759,17 +6763,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Derecha</t>
+          <t>Girar 360°</t>
         </is>
       </c>
     </row>
     <row r="91" s="8">
       <c r="A91" s="6" t="n">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Chistes</t>
+          <t>Preguntas y Respuestas</t>
         </is>
       </c>
       <c r="C91" s="6" t="n">
@@ -6777,15 +6781,19 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Chiste</t>
+          <t>Pregunta de contenido</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se dice espejo en chino?</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="n"/>
+          <t>En la tabla periódica CA representa a:</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Calcio</t>
+        </is>
+      </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
           <t>Neutral</t>
@@ -6793,7 +6801,7 @@
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>Chiste</t>
+          <t>Trivia / conocimiento</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
@@ -6803,7 +6811,7 @@
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>Chistes</t>
+          <t>Trivia</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
@@ -6823,17 +6831,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Girar 360°</t>
+          <t>Adelante</t>
         </is>
       </c>
     </row>
     <row r="92" s="8">
       <c r="A92" s="6" t="n">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Chistes</t>
+          <t>Preguntas y Respuestas</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
@@ -6841,15 +6849,19 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Chiste</t>
+          <t>Pregunta de contenido</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>¿Dónde cuelga Superman su supercapa?</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="n"/>
+          <t>Nombre de los Niños Héroes</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Agustín Melgar Fernando Montes de Oca Francisco Márquez Juan de la Barrera Juan Escutia Vicente Suárez</t>
+        </is>
+      </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
           <t>Neutral</t>
@@ -6857,7 +6869,7 @@
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>Chiste</t>
+          <t>Trivia / conocimiento</t>
         </is>
       </c>
       <c r="I92" s="6" t="inlineStr">
@@ -6867,7 +6879,7 @@
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>Chistes</t>
+          <t>Trivia</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
@@ -6887,17 +6899,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Adelante</t>
+          <t>Atrás</t>
         </is>
       </c>
     </row>
     <row r="93" s="8">
       <c r="A93" s="6" t="n">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Chistes</t>
+          <t>Preguntas y Respuestas</t>
         </is>
       </c>
       <c r="C93" s="6" t="n">
@@ -6905,15 +6917,19 @@
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Chiste</t>
+          <t>Pregunta de contenido</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>¿Qué coche usa Papá Noel?</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="n"/>
+          <t>Quién va a la cárcel: ¿el imputado, el acusado, el condenado?</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Condenado</t>
+        </is>
+      </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
           <t>Neutral</t>
@@ -6921,7 +6937,7 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>Chiste</t>
+          <t>Trivia / conocimiento</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
@@ -6931,7 +6947,7 @@
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>Chistes</t>
+          <t>Trivia</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
@@ -6951,17 +6967,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Izquierda</t>
         </is>
       </c>
     </row>
     <row r="94" s="8">
       <c r="A94" s="6" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Chistes</t>
+          <t>Preguntas y Respuestas</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
@@ -6969,15 +6985,19 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Chiste</t>
+          <t>Pregunta de contenido</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>¿Qué le dice una iguana a su hermana gemela?</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="n"/>
+          <t>Qué son los humanos: ¿omnívoros, herbívoros o carnívoros?</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Omnívoros</t>
+        </is>
+      </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
           <t>Neutral</t>
@@ -6985,7 +7005,7 @@
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>Chiste</t>
+          <t>Trivia / conocimiento</t>
         </is>
       </c>
       <c r="I94" s="6" t="inlineStr">
@@ -6995,7 +7015,7 @@
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>Chistes</t>
+          <t>Trivia</t>
         </is>
       </c>
       <c r="K94" s="6" t="inlineStr">
@@ -7015,13 +7035,13 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Izquierda</t>
+          <t>Derecha</t>
         </is>
       </c>
     </row>
     <row r="95" s="8">
       <c r="A95" s="6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
@@ -7029,7 +7049,7 @@
         </is>
       </c>
       <c r="C95" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -7038,12 +7058,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>El triángulo que tiene sus tres lados iguales ¿Cómo se llama?</t>
+          <t>Si 50 es el 100%, ¿cuánto es el 90%?</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>Equilátero</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
@@ -7089,7 +7109,7 @@
     </row>
     <row r="96" s="8">
       <c r="A96" s="6" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
@@ -7097,7 +7117,7 @@
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
@@ -7106,12 +7126,12 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>En la tabla periódica CA representa a:</t>
+          <t>¿A que esta asociada la campana de Gauss?</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>Calcio</t>
+          <t>probabilidades</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -7157,7 +7177,7 @@
     </row>
     <row r="97" s="8">
       <c r="A97" s="6" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
@@ -7165,7 +7185,7 @@
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
@@ -7174,12 +7194,12 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Nombre de los Niños Héroes</t>
+          <t>¿A quién le crecía la nariz cuando mentía?</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Agustín Melgar Fernando Montes de Oca Francisco Márquez Juan de la Barrera Juan Escutia Vicente Suárez</t>
+          <t>Pinocho</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
@@ -7225,7 +7245,7 @@
     </row>
     <row r="98" s="8">
       <c r="A98" s="6" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
@@ -7233,7 +7253,7 @@
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
@@ -7242,12 +7262,12 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Quién va a la cárcel: ¿el imputado, el acusado, el condenado?</t>
+          <t>¿A qué país pertenece la ciudad de Varsovia?</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Condenado</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -7293,7 +7313,7 @@
     </row>
     <row r="99" s="8">
       <c r="A99" s="6" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
@@ -7301,7 +7321,7 @@
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
@@ -7310,12 +7330,12 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>Qué son los humanos: ¿omnívoros, herbívoros o carnívoros?</t>
+          <t>¿A qué país pertenecen los cariocas?</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>Omnívoros</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
@@ -7361,7 +7381,7 @@
     </row>
     <row r="100" s="8">
       <c r="A100" s="6" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
@@ -7369,7 +7389,7 @@
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
@@ -7378,12 +7398,12 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Si 50 es el 100%, ¿cuánto es el 90%?</t>
+          <t>¿Con cuántos países hace frontera México?</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -7429,7 +7449,7 @@
     </row>
     <row r="101" s="8">
       <c r="A101" s="6" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
@@ -7437,7 +7457,7 @@
         </is>
       </c>
       <c r="C101" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
@@ -7446,12 +7466,12 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>¿A que esta asociada la campana de Gauss?</t>
+          <t>¿Con qué se fabricaba el pergamino?</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>probabilidades</t>
+          <t>Piel de animales</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
@@ -7497,7 +7517,7 @@
     </row>
     <row r="102" s="8">
       <c r="A102" s="6" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
@@ -7505,7 +7525,7 @@
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
@@ -7514,12 +7534,12 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>¿A quién le crecía la nariz cuando mentía?</t>
+          <t>¿Cuantos huesos tiene en el cuerpo humano de un adulto?</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Pinocho</t>
+          <t>206</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -7565,7 +7585,7 @@
     </row>
     <row r="103" s="8">
       <c r="A103" s="6" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
@@ -7573,7 +7593,7 @@
         </is>
       </c>
       <c r="C103" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
@@ -7582,12 +7602,12 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>¿A qué país pertenece la ciudad de Varsovia?</t>
+          <t>¿Cuál es el animal que tiene mayor facilidad para repetir las frases y palabras que escucha?</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>Polonia</t>
+          <t>Loro Cuervo</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
@@ -7633,7 +7653,7 @@
     </row>
     <row r="104" s="8">
       <c r="A104" s="6" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
@@ -7641,7 +7661,7 @@
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
@@ -7650,12 +7670,12 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>¿A qué país pertenecen los cariocas?</t>
+          <t>¿Cuál es el ave voladora más grande del mundo en la actualidad?</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Cóndor andino</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -7701,7 +7721,7 @@
     </row>
     <row r="105" s="8">
       <c r="A105" s="6" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
@@ -7709,7 +7729,7 @@
         </is>
       </c>
       <c r="C105" s="6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
@@ -7718,12 +7738,12 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>¿Con cuántos países hace frontera México?</t>
+          <t>¿Cuál es el ave voladora más pesada del mundo en la actualidad?</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Avutarda kori</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
@@ -7769,7 +7789,7 @@
     </row>
     <row r="106" s="8">
       <c r="A106" s="6" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
@@ -7777,7 +7797,7 @@
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
@@ -7786,12 +7806,12 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>¿Con qué se fabricaba el pergamino?</t>
+          <t>¿Cuál es el color que representa la esperanza?</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Piel de animales</t>
+          <t>Verde</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -7837,7 +7857,7 @@
     </row>
     <row r="107" s="8">
       <c r="A107" s="6" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
@@ -7845,7 +7865,7 @@
         </is>
       </c>
       <c r="C107" s="6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
@@ -7854,12 +7874,12 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>¿Cuantos huesos tiene en el cuerpo humano de un adulto?</t>
+          <t>¿Cuál es el disco más vendido de la historia?</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>Thriller</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
@@ -7905,7 +7925,7 @@
     </row>
     <row r="108" s="8">
       <c r="A108" s="6" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
@@ -7913,7 +7933,7 @@
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
@@ -7922,12 +7942,12 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el animal que tiene mayor facilidad para repetir las frases y palabras que escucha?</t>
+          <t>¿Cuál es el estado más grande de México?</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Loro Cuervo</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -7973,7 +7993,7 @@
     </row>
     <row r="109" s="8">
       <c r="A109" s="6" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
@@ -7981,7 +8001,7 @@
         </is>
       </c>
       <c r="C109" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
@@ -7990,12 +8010,12 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el ave voladora más grande del mundo en la actualidad?</t>
+          <t>¿Cuál es el idioma más antiguo de los que sobreviven en Europa?</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>Cóndor andino</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
@@ -8041,7 +8061,7 @@
     </row>
     <row r="110" s="8">
       <c r="A110" s="6" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
@@ -8049,7 +8069,7 @@
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
@@ -8058,12 +8078,12 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el ave voladora más pesada del mundo en la actualidad?</t>
+          <t>¿Cuál es el libro sagrado del Islam?</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Avutarda kori</t>
+          <t>corán</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -8109,7 +8129,7 @@
     </row>
     <row r="111" s="8">
       <c r="A111" s="6" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
@@ -8117,7 +8137,7 @@
         </is>
       </c>
       <c r="C111" s="6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
@@ -8126,12 +8146,12 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el color que representa la esperanza?</t>
+          <t>¿Cuál es el lugar más frío de la tierra?</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>Verde</t>
+          <t>Antártida</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
@@ -8177,7 +8197,7 @@
     </row>
     <row r="112" s="8">
       <c r="A112" s="6" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
@@ -8185,7 +8205,7 @@
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
@@ -8194,12 +8214,12 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el disco más vendido de la historia?</t>
+          <t>¿Cuál es el metal más caro del mundo?</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Thriller</t>
+          <t>Rodio</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -8245,7 +8265,7 @@
     </row>
     <row r="113" s="8">
       <c r="A113" s="6" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
@@ -8253,7 +8273,7 @@
         </is>
       </c>
       <c r="C113" s="6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
@@ -8262,12 +8282,12 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el estado más grande de México?</t>
+          <t>¿Cuál es el nombre de la lengua oficial en china?</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>Chihuahua</t>
+          <t>Mandarín</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
@@ -8313,7 +8333,7 @@
     </row>
     <row r="114" s="8">
       <c r="A114" s="6" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
@@ -8321,7 +8341,7 @@
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
@@ -8330,12 +8350,12 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el idioma más antiguo de los que sobreviven en Europa?</t>
+          <t>¿Cuál es el océano más grande?</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>El Océano Pacífico</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -8381,7 +8401,7 @@
     </row>
     <row r="115" s="8">
       <c r="A115" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
@@ -8389,7 +8409,7 @@
         </is>
       </c>
       <c r="C115" s="6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
@@ -8398,12 +8418,12 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el libro sagrado del Islam?</t>
+          <t>¿Cuál es el país con mayor porcentaje de budistas?</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>corán</t>
+          <t>Camboya</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
@@ -8449,7 +8469,7 @@
     </row>
     <row r="116" s="8">
       <c r="A116" s="6" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
@@ -8457,7 +8477,7 @@
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
@@ -8466,12 +8486,12 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el lugar más frío de la tierra?</t>
+          <t>¿Cuál es el país con más camellos salvajes?</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Antártida</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -8517,7 +8537,7 @@
     </row>
     <row r="117" s="8">
       <c r="A117" s="6" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
@@ -8525,7 +8545,7 @@
         </is>
       </c>
       <c r="C117" s="6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
@@ -8534,12 +8554,12 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el metal más caro del mundo?</t>
+          <t>¿Cuál es el país más grande del mundo?</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>Rodio</t>
+          <t>Rusia</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
@@ -8585,7 +8605,7 @@
     </row>
     <row r="118" s="8">
       <c r="A118" s="6" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
@@ -8593,7 +8613,7 @@
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
@@ -8602,12 +8622,12 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el nombre de la lengua oficial en china?</t>
+          <t>¿Cuál es el primero de la lista de los números primos?</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Mandarín</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -8653,7 +8673,7 @@
     </row>
     <row r="119" s="8">
       <c r="A119" s="6" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
@@ -8661,7 +8681,7 @@
         </is>
       </c>
       <c r="C119" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
@@ -8670,12 +8690,12 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el océano más grande?</t>
+          <t>¿Cuál es el río más largo del mundo?</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>El Océano Pacífico</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
@@ -8721,7 +8741,7 @@
     </row>
     <row r="120" s="8">
       <c r="A120" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
@@ -8729,7 +8749,7 @@
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
@@ -8738,12 +8758,12 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el país con mayor porcentaje de budistas?</t>
+          <t>¿Cuál es el área del arte protagonista en los Premios Óscar?</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Camboya</t>
+          <t>Cine</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -8789,7 +8809,7 @@
     </row>
     <row r="121" s="8">
       <c r="A121" s="6" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
@@ -8797,7 +8817,7 @@
         </is>
       </c>
       <c r="C121" s="6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
@@ -8806,12 +8826,12 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el país con más camellos salvajes?</t>
+          <t>¿Cuál es el área del arte protagonista en los premios Grammy?</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Música</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
@@ -8857,7 +8877,7 @@
     </row>
     <row r="122" s="8">
       <c r="A122" s="6" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
@@ -8865,7 +8885,7 @@
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
@@ -8874,12 +8894,12 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el país más grande del mundo?</t>
+          <t>¿Cuál es el único mamífero capaz de volar?</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Rusia</t>
+          <t>Murciélago</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -8925,7 +8945,7 @@
     </row>
     <row r="123" s="8">
       <c r="A123" s="6" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
@@ -8933,7 +8953,7 @@
         </is>
       </c>
       <c r="C123" s="6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
@@ -8942,12 +8962,12 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el primero de la lista de los números primos?</t>
+          <t>¿Cuál es la capital de Argentina?</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
@@ -8993,7 +9013,7 @@
     </row>
     <row r="124" s="8">
       <c r="A124" s="6" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
@@ -9001,7 +9021,7 @@
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
@@ -9010,12 +9030,12 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el río más largo del mundo?</t>
+          <t>¿Cuál es la capital de Canadá?</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -9061,7 +9081,7 @@
     </row>
     <row r="125" s="8">
       <c r="A125" s="6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
@@ -9069,7 +9089,7 @@
         </is>
       </c>
       <c r="C125" s="6" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
@@ -9078,12 +9098,12 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el área del arte protagonista en los Premios Óscar?</t>
+          <t>¿Cuál es la capital de Colombia?</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>Cine</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
@@ -9129,7 +9149,7 @@
     </row>
     <row r="126" s="8">
       <c r="A126" s="6" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
@@ -9137,7 +9157,7 @@
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
@@ -9146,12 +9166,12 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el área del arte protagonista en los premios Grammy?</t>
+          <t>¿Cuál es la capital de Croacia?</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Música</t>
+          <t>Zagreb</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -9197,7 +9217,7 @@
     </row>
     <row r="127" s="8">
       <c r="A127" s="6" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
@@ -9205,7 +9225,7 @@
         </is>
       </c>
       <c r="C127" s="6" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
@@ -9214,12 +9234,12 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es el único mamífero capaz de volar?</t>
+          <t>¿Cuál es la capital de Dinamarca?</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>Murciélago</t>
+          <t>Copenhague</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
@@ -9265,7 +9285,7 @@
     </row>
     <row r="128" s="8">
       <c r="A128" s="6" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
@@ -9273,7 +9293,7 @@
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
@@ -9282,12 +9302,12 @@
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la capital de Argentina?</t>
+          <t>¿Cuál es la capital de EU?</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -9333,7 +9353,7 @@
     </row>
     <row r="129" s="8">
       <c r="A129" s="6" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
@@ -9341,7 +9361,7 @@
         </is>
       </c>
       <c r="C129" s="6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
@@ -9350,12 +9370,12 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la capital de Canadá?</t>
+          <t>¿Cuál es la capital de España?</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
@@ -9401,7 +9421,7 @@
     </row>
     <row r="130" s="8">
       <c r="A130" s="6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
@@ -9409,7 +9429,7 @@
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
@@ -9418,12 +9438,12 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la capital de Colombia?</t>
+          <t>¿Cuál es la capital de Francia?</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>París</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -9469,7 +9489,7 @@
     </row>
     <row r="131" s="8">
       <c r="A131" s="6" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
@@ -9477,7 +9497,7 @@
         </is>
       </c>
       <c r="C131" s="6" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
@@ -9486,12 +9506,12 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la capital de Croacia?</t>
+          <t>¿Cuál es la capital de Perú?</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>Zagreb</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
@@ -9537,7 +9557,7 @@
     </row>
     <row r="132" s="8">
       <c r="A132" s="6" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
@@ -9545,7 +9565,7 @@
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
@@ -9554,12 +9574,12 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la capital de Dinamarca?</t>
+          <t>¿Cuál es la capital de Rusia?</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Copenhague</t>
+          <t>Moscú</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -9605,7 +9625,7 @@
     </row>
     <row r="133" s="8">
       <c r="A133" s="6" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
@@ -9613,7 +9633,7 @@
         </is>
       </c>
       <c r="C133" s="6" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
@@ -9622,12 +9642,12 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la capital de EU?</t>
+          <t>¿Cuál es la ciudad de los rascacielos?</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Nueva York</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
@@ -9673,7 +9693,7 @@
     </row>
     <row r="134" s="8">
       <c r="A134" s="6" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
@@ -9681,7 +9701,7 @@
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
@@ -9690,12 +9710,12 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la capital de España?</t>
+          <t>¿Cuál es la moneda del Reino Unido?</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>libra</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -9741,7 +9761,7 @@
     </row>
     <row r="135" s="8">
       <c r="A135" s="6" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
@@ -9749,7 +9769,7 @@
         </is>
       </c>
       <c r="C135" s="6" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
@@ -9758,12 +9778,12 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la capital de Francia?</t>
+          <t>¿Cuál es la moneda oficial de Estados Unidos?</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>París</t>
+          <t>Dólar</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
@@ -9809,7 +9829,7 @@
     </row>
     <row r="136" s="8">
       <c r="A136" s="6" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
@@ -9817,7 +9837,7 @@
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
@@ -9826,12 +9846,12 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la capital de Perú?</t>
+          <t>¿Cuál es la montaña más alta del mundo?</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Everest</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
@@ -9877,7 +9897,7 @@
     </row>
     <row r="137" s="8">
       <c r="A137" s="6" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
@@ -9885,7 +9905,7 @@
         </is>
       </c>
       <c r="C137" s="6" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
@@ -9894,12 +9914,12 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la capital de Rusia?</t>
+          <t>¿Cuál es la nacionalidad de Pablo Neruda?</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>Moscú</t>
+          <t>Chileno Chile</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
@@ -9945,7 +9965,7 @@
     </row>
     <row r="138" s="8">
       <c r="A138" s="6" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
@@ -9953,7 +9973,7 @@
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
@@ -9962,12 +9982,12 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la ciudad de los rascacielos?</t>
+          <t>¿Cuál es país más poblado de la Tierra?</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Nueva York</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -10013,7 +10033,7 @@
     </row>
     <row r="139" s="8">
       <c r="A139" s="6" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
@@ -10021,7 +10041,7 @@
         </is>
       </c>
       <c r="C139" s="6" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
@@ -10030,12 +10050,12 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la moneda del Reino Unido?</t>
+          <t>¿Cuál es tercer planeta en el sistema solar?</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>libra</t>
+          <t>Tierra</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
@@ -10081,7 +10101,7 @@
     </row>
     <row r="140" s="8">
       <c r="A140" s="6" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
@@ -10089,7 +10109,7 @@
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
@@ -10098,12 +10118,12 @@
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la moneda oficial de Estados Unidos?</t>
+          <t>¿Cuál fue el primer metal que empleó el hombre?</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Dólar</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
@@ -10149,7 +10169,7 @@
     </row>
     <row r="141" s="8">
       <c r="A141" s="6" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
@@ -10157,7 +10177,7 @@
         </is>
       </c>
       <c r="C141" s="6" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
@@ -10166,12 +10186,12 @@
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la montaña más alta del mundo?</t>
+          <t>¿Cuáles son las notas musicales?</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>Everest</t>
+          <t>Do re mi fa sol la si</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
@@ -10217,7 +10237,7 @@
     </row>
     <row r="142" s="8">
       <c r="A142" s="6" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
@@ -10225,7 +10245,7 @@
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
@@ -10234,12 +10254,12 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es la nacionalidad de Pablo Neruda?</t>
+          <t>¿Cuáles son los cinco tipos de sabores primarios?</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Chileno Chile</t>
+          <t>dulce amargo ácido salado umami</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
@@ -10285,7 +10305,7 @@
     </row>
     <row r="143" s="8">
       <c r="A143" s="6" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
@@ -10293,7 +10313,7 @@
         </is>
       </c>
       <c r="C143" s="6" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
@@ -10302,12 +10322,12 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es país más poblado de la Tierra?</t>
+          <t>¿Cuáles son los dos países con mayor cantidad de musulmanes?</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Indonesia India</t>
         </is>
       </c>
       <c r="G143" s="6" t="inlineStr">
@@ -10353,7 +10373,7 @@
     </row>
     <row r="144" s="8">
       <c r="A144" s="6" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
@@ -10361,7 +10381,7 @@
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
@@ -10370,12 +10390,12 @@
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál es tercer planeta en el sistema solar?</t>
+          <t>¿Cuándo acabó la II Guerra Mundial?</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Tierra</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
@@ -10421,7 +10441,7 @@
     </row>
     <row r="145" s="8">
       <c r="A145" s="6" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
@@ -10429,7 +10449,7 @@
         </is>
       </c>
       <c r="C145" s="6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
@@ -10438,12 +10458,12 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>¿Cuál fue el primer metal que empleó el hombre?</t>
+          <t>¿Cuándo empezó la Primera Guerra Mundial?</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="G145" s="6" t="inlineStr">
@@ -10489,7 +10509,7 @@
     </row>
     <row r="146" s="8">
       <c r="A146" s="6" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
@@ -10497,7 +10517,7 @@
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
@@ -10506,12 +10526,12 @@
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>¿Cuáles son las notas musicales?</t>
+          <t>¿Cuándo se extinguieron los mamuts?</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Do re mi fa sol la si</t>
+          <t>4000 años</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -10557,7 +10577,7 @@
     </row>
     <row r="147" s="8">
       <c r="A147" s="6" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
@@ -10565,7 +10585,7 @@
         </is>
       </c>
       <c r="C147" s="6" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
@@ -10574,12 +10594,12 @@
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>¿Cuáles son los cinco tipos de sabores primarios?</t>
+          <t>¿Cuántas patas tiene la araña?</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>dulce amargo ácido salado umami</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
@@ -10625,7 +10645,7 @@
     </row>
     <row r="148" s="8">
       <c r="A148" s="6" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
@@ -10633,7 +10653,7 @@
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
@@ -10642,12 +10662,12 @@
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>¿Cuáles son los dos países con mayor cantidad de musulmanes?</t>
+          <t>¿Cuánto vale el número pi?</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Indonesia India</t>
+          <t>3,1416</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
@@ -10693,7 +10713,7 @@
     </row>
     <row r="149" s="8">
       <c r="A149" s="6" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
@@ -10701,7 +10721,7 @@
         </is>
       </c>
       <c r="C149" s="6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
@@ -10710,12 +10730,12 @@
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>¿Cuándo acabó la II Guerra Mundial?</t>
+          <t>¿Cuántos años tiene un lustro?</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G149" s="6" t="inlineStr">
@@ -10761,7 +10781,7 @@
     </row>
     <row r="150" s="8">
       <c r="A150" s="6" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
@@ -10769,7 +10789,7 @@
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
@@ -10778,12 +10798,12 @@
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>¿Cuándo empezó la Primera Guerra Mundial?</t>
+          <t>¿Cuántos corazones tienen los pulpos?</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
@@ -10829,7 +10849,7 @@
     </row>
     <row r="151" s="8">
       <c r="A151" s="6" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
@@ -10837,7 +10857,7 @@
         </is>
       </c>
       <c r="C151" s="6" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
@@ -10846,12 +10866,12 @@
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>¿Cuándo se extinguieron los mamuts?</t>
+          <t>¿Cómo le llaman a los textos de autores desconocidos?</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>4000 años</t>
+          <t>Anónimo</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
@@ -10897,7 +10917,7 @@
     </row>
     <row r="152" s="8">
       <c r="A152" s="6" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
@@ -10905,7 +10925,7 @@
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
@@ -10914,12 +10934,12 @@
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>¿Cuántas patas tiene la araña?</t>
+          <t>¿Cómo se denomina el resultado de la multiplicación?</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Producto</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
@@ -10965,7 +10985,7 @@
     </row>
     <row r="153" s="8">
       <c r="A153" s="6" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
@@ -10973,7 +10993,7 @@
         </is>
       </c>
       <c r="C153" s="6" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
@@ -10982,12 +11002,12 @@
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>¿Cuánto vale el número pi?</t>
+          <t>¿Cómo se le llama a una colección de revistas, diarios y publicaciones periódicas?</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>3,1416</t>
+          <t>Hemeroteca</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
@@ -11033,7 +11053,7 @@
     </row>
     <row r="154" s="8">
       <c r="A154" s="6" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
@@ -11041,7 +11061,7 @@
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
@@ -11050,12 +11070,12 @@
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>¿Cuántos años tiene un lustro?</t>
+          <t>¿Cómo se llama el animal más rápido del mundo?</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Guepardo</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
@@ -11101,7 +11121,7 @@
     </row>
     <row r="155" s="8">
       <c r="A155" s="6" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
@@ -11109,7 +11129,7 @@
         </is>
       </c>
       <c r="C155" s="6" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
@@ -11118,12 +11138,12 @@
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>¿Cuántos corazones tienen los pulpos?</t>
+          <t>¿Cómo se llama el estadio del F.C. Barcelona?</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Camp Nou</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
@@ -11169,7 +11189,7 @@
     </row>
     <row r="156" s="8">
       <c r="A156" s="6" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
@@ -11177,7 +11197,7 @@
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
@@ -11186,12 +11206,12 @@
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo le llaman a los textos de autores desconocidos?</t>
+          <t>¿Cómo se llama el fundador de Facebook?</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Anónimo</t>
+          <t>Mark Zuckerberg</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
@@ -11237,7 +11257,7 @@
     </row>
     <row r="157" s="8">
       <c r="A157" s="6" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
@@ -11245,7 +11265,7 @@
         </is>
       </c>
       <c r="C157" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
@@ -11254,12 +11274,12 @@
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se denomina el resultado de la multiplicación?</t>
+          <t>¿Cómo se llama el himno nacional de Francia?</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>Producto</t>
+          <t>La Marsellesa</t>
         </is>
       </c>
       <c r="G157" s="6" t="inlineStr">
@@ -11305,7 +11325,7 @@
     </row>
     <row r="158" s="8">
       <c r="A158" s="6" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
@@ -11313,7 +11333,7 @@
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
@@ -11322,12 +11342,12 @@
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se le llama a una colección de revistas, diarios y publicaciones periódicas?</t>
+          <t>¿Cómo se llama el nuevo presidente de los Estados Unidos?</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Hemeroteca</t>
+          <t>Donald Trump</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
@@ -11373,7 +11393,7 @@
     </row>
     <row r="159" s="8">
       <c r="A159" s="6" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
@@ -11381,7 +11401,7 @@
         </is>
       </c>
       <c r="C159" s="6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
@@ -11390,12 +11410,12 @@
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama el animal más rápido del mundo?</t>
+          <t>¿Cómo se llama el procedimiento de subir la bandera?</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>Guepardo</t>
+          <t>Izar</t>
         </is>
       </c>
       <c r="G159" s="6" t="inlineStr">
@@ -11441,7 +11461,7 @@
     </row>
     <row r="160" s="8">
       <c r="A160" s="6" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
@@ -11449,7 +11469,7 @@
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
@@ -11458,12 +11478,12 @@
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama el estadio del F.C. Barcelona?</t>
+          <t>¿Cómo se llama el proceso por el cual las plantas obtienen alimento?</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Camp Nou</t>
+          <t>Fotosíntesis</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
@@ -11509,7 +11529,7 @@
     </row>
     <row r="161" s="8">
       <c r="A161" s="6" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
@@ -11517,7 +11537,7 @@
         </is>
       </c>
       <c r="C161" s="6" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
@@ -11526,12 +11546,12 @@
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama el fundador de Facebook?</t>
+          <t>¿Cómo se llama la Reina del Reino Unido?</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg</t>
+          <t>Isabel Segunda</t>
         </is>
       </c>
       <c r="G161" s="6" t="inlineStr">
@@ -11577,7 +11597,7 @@
     </row>
     <row r="162" s="8">
       <c r="A162" s="6" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
@@ -11585,7 +11605,7 @@
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
@@ -11594,12 +11614,12 @@
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama el himno nacional de Francia?</t>
+          <t>¿Cómo se llama la capital de Mongolia?</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>La Marsellesa</t>
+          <t>Ulan Bator</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
@@ -11645,7 +11665,7 @@
     </row>
     <row r="163" s="8">
       <c r="A163" s="6" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
@@ -11653,7 +11673,7 @@
         </is>
       </c>
       <c r="C163" s="6" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
@@ -11662,12 +11682,12 @@
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama el nuevo presidente de los Estados Unidos?</t>
+          <t>¿Cómo se llama la energía contenida en el núcleo de los átomos?</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>Donald Trump</t>
+          <t>Energía nuclear</t>
         </is>
       </c>
       <c r="G163" s="6" t="inlineStr">
@@ -11713,7 +11733,7 @@
     </row>
     <row r="164" s="8">
       <c r="A164" s="6" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
@@ -11721,7 +11741,7 @@
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
@@ -11730,12 +11750,12 @@
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama el procedimiento de subir la bandera?</t>
+          <t>¿Cómo se llama la estación espacial rusa?</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Izar</t>
+          <t>Mir</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
@@ -11781,7 +11801,7 @@
     </row>
     <row r="165" s="8">
       <c r="A165" s="6" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
@@ -11789,7 +11809,7 @@
         </is>
       </c>
       <c r="C165" s="6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
@@ -11798,12 +11818,12 @@
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama el proceso por el cual las plantas obtienen alimento?</t>
+          <t>¿De qué colores es la bandera de México?</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>Fotosíntesis</t>
+          <t>Verde blanco rojo</t>
         </is>
       </c>
       <c r="G165" s="6" t="inlineStr">
@@ -11849,7 +11869,7 @@
     </row>
     <row r="166" s="8">
       <c r="A166" s="6" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
@@ -11857,7 +11877,7 @@
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
@@ -11866,12 +11886,12 @@
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama la Reina del Reino Unido?</t>
+          <t>¿De qué estado fue emperador Napoleón Bonaparte?</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Isabel Segunda</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
@@ -11917,7 +11937,7 @@
     </row>
     <row r="167" s="8">
       <c r="A167" s="6" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
@@ -11925,7 +11945,7 @@
         </is>
       </c>
       <c r="C167" s="6" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
@@ -11934,12 +11954,12 @@
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama la capital de Mongolia?</t>
+          <t>¿De qué estilo arquitectónico es la Catedral de Notre Dame en París?</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>Ulan Bator</t>
+          <t>Gótico</t>
         </is>
       </c>
       <c r="G167" s="6" t="inlineStr">
@@ -11985,7 +12005,7 @@
     </row>
     <row r="168" s="8">
       <c r="A168" s="6" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
@@ -11993,7 +12013,7 @@
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
@@ -12002,12 +12022,12 @@
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama la energía contenida en el núcleo de los átomos?</t>
+          <t>¿De qué está recubierto el cuerpo de los peces?</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Energía nuclear</t>
+          <t>Escamas</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
@@ -12053,7 +12073,7 @@
     </row>
     <row r="169" s="8">
       <c r="A169" s="6" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
@@ -12061,7 +12081,7 @@
         </is>
       </c>
       <c r="C169" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
@@ -12070,12 +12090,12 @@
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>¿Cómo se llama la estación espacial rusa?</t>
+          <t>¿De qué lengua proviene el español?</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>Mir</t>
+          <t>Latín</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
@@ -12121,7 +12141,7 @@
     </row>
     <row r="170" s="8">
       <c r="A170" s="6" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
@@ -12129,7 +12149,7 @@
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
@@ -12138,12 +12158,12 @@
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>¿De qué colores es la bandera de México?</t>
+          <t>¿De qué país es el futbolista Zlatan Ibrahimović?</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Verde blanco rojo</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
@@ -12189,7 +12209,7 @@
     </row>
     <row r="171" s="8">
       <c r="A171" s="6" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
@@ -12197,7 +12217,7 @@
         </is>
       </c>
       <c r="C171" s="6" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
@@ -12206,12 +12226,12 @@
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>¿De qué estado fue emperador Napoleón Bonaparte?</t>
+          <t>¿Dónde está la Casa Blanca?</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="G171" s="6" t="inlineStr">
@@ -12257,7 +12277,7 @@
     </row>
     <row r="172" s="8">
       <c r="A172" s="6" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
@@ -12265,7 +12285,7 @@
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
@@ -12274,12 +12294,12 @@
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>¿De qué estilo arquitectónico es la Catedral de Notre Dame en París?</t>
+          <t>¿Dónde originaron los juegos olímpicos?</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Gótico</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -12325,7 +12345,7 @@
     </row>
     <row r="173" s="8">
       <c r="A173" s="6" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
@@ -12333,7 +12353,7 @@
         </is>
       </c>
       <c r="C173" s="6" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
@@ -12342,12 +12362,12 @@
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>¿De qué está recubierto el cuerpo de los peces?</t>
+          <t>¿Dónde se encuentra la Sagrada Familia?</t>
         </is>
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>Escamas</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G173" s="6" t="inlineStr">
@@ -12393,7 +12413,7 @@
     </row>
     <row r="174" s="8">
       <c r="A174" s="6" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
@@ -12401,7 +12421,7 @@
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
@@ -12410,12 +12430,12 @@
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>¿De qué lengua proviene el español?</t>
+          <t>¿Dónde se encuentra la capa de ozono?</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Latín</t>
+          <t>Atmósfera</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -12461,7 +12481,7 @@
     </row>
     <row r="175" s="8">
       <c r="A175" s="6" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
@@ -12469,7 +12489,7 @@
         </is>
       </c>
       <c r="C175" s="6" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
@@ -12478,12 +12498,12 @@
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>¿De qué país es el futbolista Zlatan Ibrahimović?</t>
+          <t>¿Dónde se encuentra la famosa Torre Eiffel?</t>
         </is>
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>París, Francia</t>
         </is>
       </c>
       <c r="G175" s="6" t="inlineStr">
@@ -12529,7 +12549,7 @@
     </row>
     <row r="176" s="8">
       <c r="A176" s="6" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
@@ -12537,7 +12557,7 @@
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
@@ -12546,12 +12566,12 @@
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>¿Dónde está la Casa Blanca?</t>
+          <t>¿En que fecha ocurrió la masacre de Tlatelolco?</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>2 de octubre de 1968</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
@@ -12597,7 +12617,7 @@
     </row>
     <row r="177" s="8">
       <c r="A177" s="6" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
@@ -12605,7 +12625,7 @@
         </is>
       </c>
       <c r="C177" s="6" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
@@ -12614,12 +12634,12 @@
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>¿Dónde originaron los juegos olímpicos?</t>
+          <t>¿En qué año apareció en el mercado el primer videojuego protagonizado por Super Mario?</t>
         </is>
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>Grecia</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="G177" s="6" t="inlineStr">
@@ -12665,7 +12685,7 @@
     </row>
     <row r="178" s="8">
       <c r="A178" s="6" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
@@ -12673,7 +12693,7 @@
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
@@ -12682,12 +12702,12 @@
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>¿Dónde se encuentra la Sagrada Familia?</t>
+          <t>¿En qué año comenzó la II Guerra Mundial?</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
@@ -12733,7 +12753,7 @@
     </row>
     <row r="179" s="8">
       <c r="A179" s="6" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
@@ -12741,7 +12761,7 @@
         </is>
       </c>
       <c r="C179" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
@@ -12750,12 +12770,12 @@
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>¿Dónde se encuentra la capa de ozono?</t>
+          <t>¿En qué año se aprobó la actual Constitución española?</t>
         </is>
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>Atmósfera</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="G179" s="6" t="inlineStr">
@@ -12801,7 +12821,7 @@
     </row>
     <row r="180" s="8">
       <c r="A180" s="6" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
@@ -12809,7 +12829,7 @@
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
@@ -12818,12 +12838,12 @@
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>¿Dónde se encuentra la famosa Torre Eiffel?</t>
+          <t>¿En qué continente está Ecuador?</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>París, Francia</t>
+          <t>Américano</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
@@ -12869,7 +12889,7 @@
     </row>
     <row r="181" s="8">
       <c r="A181" s="6" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
@@ -12877,7 +12897,7 @@
         </is>
       </c>
       <c r="C181" s="6" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
@@ -12886,12 +12906,12 @@
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>¿En que fecha ocurrió la masacre de Tlatelolco?</t>
+          <t>¿En qué isla está situado el Teide?</t>
         </is>
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2 de octubre de 1968</t>
+          <t>Tenerife</t>
         </is>
       </c>
       <c r="G181" s="6" t="inlineStr">
@@ -12937,7 +12957,7 @@
     </row>
     <row r="182" s="8">
       <c r="A182" s="6" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
@@ -12945,7 +12965,7 @@
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
@@ -12954,12 +12974,12 @@
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>¿En qué año apareció en el mercado el primer videojuego protagonizado por Super Mario?</t>
+          <t>¿En qué lugar del cuerpo se produce la insulina?</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>Páncreas</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
@@ -13005,7 +13025,7 @@
     </row>
     <row r="183" s="8">
       <c r="A183" s="6" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
@@ -13013,7 +13033,7 @@
         </is>
       </c>
       <c r="C183" s="6" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
@@ -13022,12 +13042,12 @@
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>¿En qué año comenzó la II Guerra Mundial?</t>
+          <t>¿En qué país se encuentra el estadio de Wembley?</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>Reino Unido Londres</t>
         </is>
       </c>
       <c r="G183" s="6" t="inlineStr">
@@ -13073,7 +13093,7 @@
     </row>
     <row r="184" s="8">
       <c r="A184" s="6" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
@@ -13081,7 +13101,7 @@
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
@@ -13090,12 +13110,12 @@
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>¿En qué año se aprobó la actual Constitución española?</t>
+          <t>¿En qué país se encuentra el famoso monumento Taj Mahal?</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -13141,7 +13161,7 @@
     </row>
     <row r="185" s="8">
       <c r="A185" s="6" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
@@ -13149,7 +13169,7 @@
         </is>
       </c>
       <c r="C185" s="6" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
@@ -13158,12 +13178,12 @@
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>¿En qué continente está Ecuador?</t>
+          <t>¿En qué país se encuentra la Universidad de Cambridge?</t>
         </is>
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>Américano</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="G185" s="6" t="inlineStr">
@@ -13209,7 +13229,7 @@
     </row>
     <row r="186" s="8">
       <c r="A186" s="6" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
@@ -13217,7 +13237,7 @@
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
@@ -13226,12 +13246,12 @@
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>¿En qué isla está situado el Teide?</t>
+          <t>¿En qué país se encuentra la torre de Pisa?</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Tenerife</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
@@ -13277,7 +13297,7 @@
     </row>
     <row r="187" s="8">
       <c r="A187" s="6" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
@@ -13285,7 +13305,7 @@
         </is>
       </c>
       <c r="C187" s="6" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
@@ -13294,12 +13314,12 @@
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>¿En qué lugar del cuerpo se produce la insulina?</t>
+          <t>¿En qué país se usó la primera bomba atómica en combate?</t>
         </is>
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>Páncreas</t>
+          <t>Hiroshima</t>
         </is>
       </c>
       <c r="G187" s="6" t="inlineStr">
@@ -13345,7 +13365,7 @@
     </row>
     <row r="188" s="8">
       <c r="A188" s="6" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
@@ -13353,7 +13373,7 @@
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
@@ -13362,12 +13382,12 @@
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>¿En qué país se encuentra el estadio de Wembley?</t>
+          <t>¿En qué se especializa la cartografía?</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Reino Unido Londres</t>
+          <t>Mapas</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
@@ -13413,7 +13433,7 @@
     </row>
     <row r="189" s="8">
       <c r="A189" s="6" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
@@ -13421,7 +13441,7 @@
         </is>
       </c>
       <c r="C189" s="6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
@@ -13430,12 +13450,12 @@
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>¿En qué país se encuentra el famoso monumento Taj Mahal?</t>
+          <t>¿Existen animales inmortales?</t>
         </is>
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>La Medusa Turritopsis nutricula</t>
         </is>
       </c>
       <c r="G189" s="6" t="inlineStr">
@@ -13481,7 +13501,7 @@
     </row>
     <row r="190" s="8">
       <c r="A190" s="6" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
@@ -13489,7 +13509,7 @@
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
@@ -13498,12 +13518,12 @@
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>¿En qué país se encuentra la Universidad de Cambridge?</t>
+          <t>¿Quién era el general de los nazis en la Segunda Guerra Mundial?</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Adolf Hitler</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
@@ -13549,7 +13569,7 @@
     </row>
     <row r="191" s="8">
       <c r="A191" s="6" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
@@ -13557,7 +13577,7 @@
         </is>
       </c>
       <c r="C191" s="6" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
@@ -13566,12 +13586,12 @@
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>¿En qué país se encuentra la torre de Pisa?</t>
+          <t>¿Quién es Justin Timberlake?</t>
         </is>
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>Italia</t>
+          <t>cantante</t>
         </is>
       </c>
       <c r="G191" s="6" t="inlineStr">
@@ -13617,7 +13637,7 @@
     </row>
     <row r="192" s="8">
       <c r="A192" s="6" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
@@ -13625,7 +13645,7 @@
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
@@ -13634,12 +13654,12 @@
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>¿En qué país se usó la primera bomba atómica en combate?</t>
+          <t>¿Quién es el autor de el Quijote?</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Hiroshima</t>
+          <t>Miguel de Cervantes</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
@@ -13685,7 +13705,7 @@
     </row>
     <row r="193" s="8">
       <c r="A193" s="6" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
@@ -13693,7 +13713,7 @@
         </is>
       </c>
       <c r="C193" s="6" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
@@ -13702,12 +13722,12 @@
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>¿En qué se especializa la cartografía?</t>
+          <t>¿Quién es el famoso Rey de Rock en los Estados Unidos?</t>
         </is>
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>Mapas</t>
+          <t>Elvis Presley</t>
         </is>
       </c>
       <c r="G193" s="6" t="inlineStr">
@@ -13753,7 +13773,7 @@
     </row>
     <row r="194" s="8">
       <c r="A194" s="6" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
@@ -13761,7 +13781,7 @@
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
@@ -13770,12 +13790,12 @@
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>¿Existen animales inmortales?</t>
+          <t>¿Quién es el padre del psicoanálisis?</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>La Medusa Turritopsis nutricula</t>
+          <t>Sigmund Freud</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
@@ -13821,7 +13841,7 @@
     </row>
     <row r="195" s="8">
       <c r="A195" s="6" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
@@ -13829,7 +13849,7 @@
         </is>
       </c>
       <c r="C195" s="6" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
@@ -13838,12 +13858,12 @@
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>¿Quién era el general de los nazis en la Segunda Guerra Mundial?</t>
+          <t>¿Quién es el presidente de España?</t>
         </is>
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>Adolf Hitler</t>
+          <t>Pedro Sánchez</t>
         </is>
       </c>
       <c r="G195" s="6" t="inlineStr">
@@ -13889,7 +13909,7 @@
     </row>
     <row r="196" s="8">
       <c r="A196" s="6" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
@@ -13897,7 +13917,7 @@
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
@@ -13906,12 +13926,12 @@
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>¿Quién es Justin Timberlake?</t>
+          <t>¿Quién es el protagonista de la película Rocky?</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>cantante</t>
+          <t>Sylvester Stallone</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
@@ -13957,7 +13977,7 @@
     </row>
     <row r="197" s="8">
       <c r="A197" s="6" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
@@ -13965,7 +13985,7 @@
         </is>
       </c>
       <c r="C197" s="6" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
@@ -13974,12 +13994,12 @@
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>¿Quién es el autor de el Quijote?</t>
+          <t>¿Quién es el secretario general de la Organización de Naciones Unidas?</t>
         </is>
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>Miguel de Cervantes</t>
+          <t>António Gutierres</t>
         </is>
       </c>
       <c r="G197" s="6" t="inlineStr">
@@ -14025,7 +14045,7 @@
     </row>
     <row r="198" s="8">
       <c r="A198" s="6" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
@@ -14033,7 +14053,7 @@
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
@@ -14042,12 +14062,12 @@
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>¿Quién es el famoso Rey de Rock en los Estados Unidos?</t>
+          <t>¿Quién escribió Hamlet?</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Elvis Presley</t>
+          <t>William Shakespeare</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
@@ -14093,7 +14113,7 @@
     </row>
     <row r="199" s="8">
       <c r="A199" s="6" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
@@ -14101,7 +14121,7 @@
         </is>
       </c>
       <c r="C199" s="6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D199" s="6" t="inlineStr">
         <is>
@@ -14110,12 +14130,12 @@
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>¿Quién es el padre del psicoanálisis?</t>
+          <t>¿Quién escribió La Odisea?</t>
         </is>
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>Sigmund Freud</t>
+          <t>Homero</t>
         </is>
       </c>
       <c r="G199" s="6" t="inlineStr">
@@ -14161,7 +14181,7 @@
     </row>
     <row r="200" s="8">
       <c r="A200" s="6" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
@@ -14169,7 +14189,7 @@
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
@@ -14178,12 +14198,12 @@
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>¿Quién es el presidente de España?</t>
+          <t>¿Quién ganó el mundial de 2014?</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Pedro Sánchez</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -14229,7 +14249,7 @@
     </row>
     <row r="201" s="8">
       <c r="A201" s="6" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
@@ -14237,7 +14257,7 @@
         </is>
       </c>
       <c r="C201" s="6" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
@@ -14246,12 +14266,12 @@
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>¿Quién es el protagonista de la película Rocky?</t>
+          <t>¿Quién pintó “la última cena”?</t>
         </is>
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>Sylvester Stallone</t>
+          <t>Leonardo da Vinci</t>
         </is>
       </c>
       <c r="G201" s="6" t="inlineStr">
@@ -14297,7 +14317,7 @@
     </row>
     <row r="202" s="8">
       <c r="A202" s="6" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
@@ -14305,7 +14325,7 @@
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
@@ -14314,12 +14334,12 @@
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>¿Quién es el secretario general de la Organización de Naciones Unidas?</t>
+          <t>¿Quién sabía que no sabía nada?</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>António Gutierres</t>
+          <t>Platón</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
@@ -14365,7 +14385,7 @@
     </row>
     <row r="203" s="8">
       <c r="A203" s="6" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
@@ -14373,7 +14393,7 @@
         </is>
       </c>
       <c r="C203" s="6" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D203" s="6" t="inlineStr">
         <is>
@@ -14382,12 +14402,12 @@
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>¿Quién escribió Hamlet?</t>
+          <t>¿Quién traicionó a Jesús?</t>
         </is>
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>William Shakespeare</t>
+          <t>Judas</t>
         </is>
       </c>
       <c r="G203" s="6" t="inlineStr">
@@ -14433,7 +14453,7 @@
     </row>
     <row r="204" s="8">
       <c r="A204" s="6" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
@@ -14441,7 +14461,7 @@
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
@@ -14450,12 +14470,12 @@
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>¿Quién escribió La Odisea?</t>
+          <t>¿Qué año llegó Cristóbal Colón a América?</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Homero</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
@@ -14501,7 +14521,7 @@
     </row>
     <row r="205" s="8">
       <c r="A205" s="6" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
@@ -14509,7 +14529,7 @@
         </is>
       </c>
       <c r="C205" s="6" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D205" s="6" t="inlineStr">
         <is>
@@ -14518,12 +14538,12 @@
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>¿Quién ganó el mundial de 2014?</t>
+          <t>¿Qué deporte practica profesionalmente Roger Federer?</t>
         </is>
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Tenis</t>
         </is>
       </c>
       <c r="G205" s="6" t="inlineStr">
@@ -14569,7 +14589,7 @@
     </row>
     <row r="206" s="8">
       <c r="A206" s="6" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
@@ -14577,7 +14597,7 @@
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
@@ -14586,12 +14606,12 @@
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>¿Quién pintó “la última cena”?</t>
+          <t>¿Qué deporte practicaba Michael Jordan?</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci</t>
+          <t>Baloncesto</t>
         </is>
       </c>
       <c r="G206" s="6" t="inlineStr">
@@ -14637,7 +14657,7 @@
     </row>
     <row r="207" s="8">
       <c r="A207" s="6" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
@@ -14645,7 +14665,7 @@
         </is>
       </c>
       <c r="C207" s="6" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
@@ -14654,12 +14674,12 @@
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>¿Quién sabía que no sabía nada?</t>
+          <t>¿Qué día celebran los cristianos la festividad de la Epifanía de Jesús?</t>
         </is>
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>Platón</t>
+          <t>6 de enero</t>
         </is>
       </c>
       <c r="G207" s="6" t="inlineStr">
@@ -14705,7 +14725,7 @@
     </row>
     <row r="208" s="8">
       <c r="A208" s="6" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
@@ -14713,7 +14733,7 @@
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
@@ -14722,12 +14742,12 @@
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>¿Quién traicionó a Jesús?</t>
+          <t>¿Qué enfermedad padecía Stephen Hawking?</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>Judas</t>
+          <t>Esclerosis Lateral Amiotrófica</t>
         </is>
       </c>
       <c r="G208" s="6" t="inlineStr">
@@ -14773,7 +14793,7 @@
     </row>
     <row r="209" s="8">
       <c r="A209" s="6" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
@@ -14781,7 +14801,7 @@
         </is>
       </c>
       <c r="C209" s="6" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
@@ -14790,12 +14810,12 @@
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>¿Qué año llegó Cristóbal Colón a América?</t>
+          <t>¿Qué era el Concorde?</t>
         </is>
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>Avión supersónico</t>
         </is>
       </c>
       <c r="G209" s="6" t="inlineStr">
@@ -14841,7 +14861,7 @@
     </row>
     <row r="210" s="8">
       <c r="A210" s="6" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
@@ -14849,7 +14869,7 @@
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
@@ -14858,12 +14878,12 @@
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>¿Qué deporte practica profesionalmente Roger Federer?</t>
+          <t>¿Qué es más grande un átomo o una célula?</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>Tenis</t>
+          <t>célula</t>
         </is>
       </c>
       <c r="G210" s="6" t="inlineStr">
@@ -14909,7 +14929,7 @@
     </row>
     <row r="211" s="8">
       <c r="A211" s="6" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
@@ -14917,7 +14937,7 @@
         </is>
       </c>
       <c r="C211" s="6" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
@@ -14926,12 +14946,12 @@
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>¿Qué deporte practicaba Michael Jordan?</t>
+          <t>¿Qué es más pequeño, un átomo o una molécula?</t>
         </is>
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>Baloncesto</t>
+          <t>átomo</t>
         </is>
       </c>
       <c r="G211" s="6" t="inlineStr">
@@ -14977,7 +14997,7 @@
     </row>
     <row r="212" s="8">
       <c r="A212" s="6" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
@@ -14985,7 +15005,7 @@
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
@@ -14994,12 +15014,12 @@
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>¿Qué día celebran los cristianos la festividad de la Epifanía de Jesús?</t>
+          <t>¿Qué es un animal carnívoro?</t>
         </is>
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>6 de enero</t>
+          <t>Que come carne</t>
         </is>
       </c>
       <c r="G212" s="6" t="inlineStr">
@@ -15045,7 +15065,7 @@
     </row>
     <row r="213" s="8">
       <c r="A213" s="6" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
@@ -15053,7 +15073,7 @@
         </is>
       </c>
       <c r="C213" s="6" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
@@ -15062,12 +15082,12 @@
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>¿Qué enfermedad padecía Stephen Hawking?</t>
+          <t>¿Qué es un ebook?</t>
         </is>
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>Esclerosis Lateral Amiotrófica</t>
+          <t>Libro en formato digital</t>
         </is>
       </c>
       <c r="G213" s="6" t="inlineStr">
@@ -15113,7 +15133,7 @@
     </row>
     <row r="214" s="8">
       <c r="A214" s="6" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
@@ -15121,7 +15141,7 @@
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
@@ -15130,12 +15150,12 @@
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>¿Qué era el Concorde?</t>
+          <t>¿Qué es un mitómano?</t>
         </is>
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>Avión supersónico</t>
+          <t>mentiroso</t>
         </is>
       </c>
       <c r="G214" s="6" t="inlineStr">
@@ -15181,7 +15201,7 @@
     </row>
     <row r="215" s="8">
       <c r="A215" s="6" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
@@ -15189,7 +15209,7 @@
         </is>
       </c>
       <c r="C215" s="6" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
@@ -15198,12 +15218,12 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>¿Qué es más grande un átomo o una célula?</t>
+          <t>¿Qué es un ovíparo?</t>
         </is>
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>célula</t>
+          <t>Un animal que nace de un huevo</t>
         </is>
       </c>
       <c r="G215" s="6" t="inlineStr">
@@ -15249,7 +15269,7 @@
     </row>
     <row r="216" s="8">
       <c r="A216" s="6" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
@@ -15257,7 +15277,7 @@
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
@@ -15266,12 +15286,12 @@
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>¿Qué es más pequeño, un átomo o una molécula?</t>
+          <t>¿Qué grasas hacen tan saludable el aceite de oliva?</t>
         </is>
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>átomo</t>
+          <t>monoinsaturadas</t>
         </is>
       </c>
       <c r="G216" s="6" t="inlineStr">
@@ -15317,7 +15337,7 @@
     </row>
     <row r="217" s="8">
       <c r="A217" s="6" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
@@ -15325,7 +15345,7 @@
         </is>
       </c>
       <c r="C217" s="6" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
@@ -15334,12 +15354,12 @@
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>¿Qué es un animal carnívoro?</t>
+          <t>¿Qué instrumento tocaba Paco de Lucía?</t>
         </is>
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>Que come carne</t>
+          <t>Guitarra</t>
         </is>
       </c>
       <c r="G217" s="6" t="inlineStr">
@@ -15385,7 +15405,7 @@
     </row>
     <row r="218" s="8">
       <c r="A218" s="6" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
@@ -15393,7 +15413,7 @@
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
@@ -15402,12 +15422,12 @@
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>¿Qué es un ebook?</t>
+          <t>¿Qué instrumento óptico permite ver los astros de cerca?</t>
         </is>
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>Libro en formato digital</t>
+          <t>Telescopio</t>
         </is>
       </c>
       <c r="G218" s="6" t="inlineStr">
@@ -15453,7 +15473,7 @@
     </row>
     <row r="219" s="8">
       <c r="A219" s="6" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
@@ -15461,7 +15481,7 @@
         </is>
       </c>
       <c r="C219" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
@@ -15470,12 +15490,12 @@
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>¿Qué es un mitómano?</t>
+          <t>¿Qué país tiene forma de bota?</t>
         </is>
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>mentiroso</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="G219" s="6" t="inlineStr">
@@ -15521,7 +15541,7 @@
     </row>
     <row r="220" s="8">
       <c r="A220" s="6" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
@@ -15529,7 +15549,7 @@
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
@@ -15538,12 +15558,12 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>¿Qué es un ovíparo?</t>
+          <t>¿Qué producto cultiva más Guatemala?</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>Un animal que nace de un huevo</t>
+          <t>Café</t>
         </is>
       </c>
       <c r="G220" s="6" t="inlineStr">
@@ -15589,7 +15609,7 @@
     </row>
     <row r="221" s="8">
       <c r="A221" s="6" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
@@ -15597,7 +15617,7 @@
         </is>
       </c>
       <c r="C221" s="6" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D221" s="6" t="inlineStr">
         <is>
@@ -15606,12 +15626,12 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>¿Qué grasas hacen tan saludable el aceite de oliva?</t>
+          <t>¿Qué rama de la Biología estudia los animales?</t>
         </is>
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>monoinsaturadas</t>
+          <t>zoología</t>
         </is>
       </c>
       <c r="G221" s="6" t="inlineStr">
@@ -15657,7 +15677,7 @@
     </row>
     <row r="222" s="8">
       <c r="A222" s="6" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
@@ -15665,7 +15685,7 @@
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D222" s="6" t="inlineStr">
         <is>
@@ -15674,12 +15694,12 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>¿Qué instrumento tocaba Paco de Lucía?</t>
+          <t>¿Qué significa FIFA?</t>
         </is>
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>Guitarra</t>
+          <t>Federación Internacional de Fútbol Asociación</t>
         </is>
       </c>
       <c r="G222" s="6" t="inlineStr">
@@ -15725,7 +15745,7 @@
     </row>
     <row r="223" s="8">
       <c r="A223" s="6" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
@@ -15733,7 +15753,7 @@
         </is>
       </c>
       <c r="C223" s="6" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
@@ -15742,12 +15762,12 @@
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>¿Qué instrumento óptico permite ver los astros de cerca?</t>
+          <t>¿Qué tipo de animal es la ballena?</t>
         </is>
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>Telescopio</t>
+          <t>Mamífero marino</t>
         </is>
       </c>
       <c r="G223" s="6" t="inlineStr">
@@ -15793,7 +15813,7 @@
     </row>
     <row r="224" s="8">
       <c r="A224" s="6" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
@@ -15801,7 +15821,7 @@
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
@@ -15810,12 +15830,12 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>¿Qué país tiene forma de bota?</t>
+          <t>¿Qué veterano músico es la canción Tears in Heaven?</t>
         </is>
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>Italia</t>
+          <t>Eric Clapton</t>
         </is>
       </c>
       <c r="G224" s="6" t="inlineStr">
@@ -15860,481 +15880,146 @@
       </c>
     </row>
     <row r="225" s="8">
-      <c r="A225" s="6" t="n">
-        <v>235</v>
-      </c>
-      <c r="B225" s="6" t="inlineStr">
-        <is>
-          <t>Preguntas y Respuestas</t>
-        </is>
-      </c>
-      <c r="C225" s="6" t="n">
-        <v>131</v>
-      </c>
-      <c r="D225" s="6" t="inlineStr">
-        <is>
-          <t>Pregunta de contenido</t>
-        </is>
-      </c>
-      <c r="E225" s="6" t="inlineStr">
-        <is>
-          <t>¿Qué producto cultiva más Guatemala?</t>
-        </is>
-      </c>
-      <c r="F225" s="6" t="inlineStr">
-        <is>
-          <t>Café</t>
-        </is>
-      </c>
-      <c r="G225" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="H225" s="6" t="inlineStr">
-        <is>
-          <t>Trivia / conocimiento</t>
-        </is>
-      </c>
-      <c r="I225" s="6" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="J225" s="6" t="inlineStr">
-        <is>
-          <t>Trivia</t>
-        </is>
-      </c>
-      <c r="K225" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/midiacom/Ereberus-robot/blob/master/Ereberus-robot-uff-source-code/Ereberus-software-uff/db.json</t>
+      <c r="A225" t="n">
+        <v>247</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Interacción: música agregada a mano</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Interacción — Pregunta</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Te voy a poner una canción, ¿sabes cómo se llama?</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Danza Kuduro</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Feliz / Neutral / Triste</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Socialización / conversación</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Reconocimiento Musical</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Feliz</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Triste</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>danza-kuduro.mp3</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Girar 360°</t>
+          <t>Atrás</t>
         </is>
       </c>
     </row>
     <row r="226" s="8">
-      <c r="A226" s="6" t="n">
-        <v>236</v>
-      </c>
-      <c r="B226" s="6" t="inlineStr">
-        <is>
-          <t>Preguntas y Respuestas</t>
-        </is>
-      </c>
-      <c r="C226" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="D226" s="6" t="inlineStr">
-        <is>
-          <t>Pregunta de contenido</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>¿Qué rama de la Biología estudia los animales?</t>
-        </is>
-      </c>
-      <c r="F226" s="6" t="inlineStr">
-        <is>
-          <t>zoología</t>
-        </is>
-      </c>
-      <c r="G226" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="H226" s="6" t="inlineStr">
-        <is>
-          <t>Trivia / conocimiento</t>
-        </is>
-      </c>
-      <c r="I226" s="6" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="J226" s="6" t="inlineStr">
-        <is>
-          <t>Trivia</t>
-        </is>
-      </c>
-      <c r="K226" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/midiacom/Ereberus-robot/blob/master/Ereberus-robot-uff-source-code/Ereberus-software-uff/db.json</t>
+      <c r="A226" t="n">
+        <v>248</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Interacción: música agregada a mano</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Interacción — Pregunta</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Escuchá esto, ¿qué canción es?</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>More Than Words</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Feliz / Neutral / Triste</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Socialización / conversación</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Reconocimiento Musical</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Feliz</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Triste</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>more-than-words-heaven.mp3</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Adelante</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" s="8">
-      <c r="A227" s="6" t="n">
-        <v>237</v>
-      </c>
-      <c r="B227" s="6" t="inlineStr">
-        <is>
-          <t>Preguntas y Respuestas</t>
-        </is>
-      </c>
-      <c r="C227" s="6" t="n">
-        <v>133</v>
-      </c>
-      <c r="D227" s="6" t="inlineStr">
-        <is>
-          <t>Pregunta de contenido</t>
-        </is>
-      </c>
-      <c r="E227" s="6" t="inlineStr">
-        <is>
-          <t>¿Qué significa FIFA?</t>
-        </is>
-      </c>
-      <c r="F227" s="6" t="inlineStr">
-        <is>
-          <t>Federación Internacional de Fútbol Asociación</t>
-        </is>
-      </c>
-      <c r="G227" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="H227" s="6" t="inlineStr">
-        <is>
-          <t>Trivia / conocimiento</t>
-        </is>
-      </c>
-      <c r="I227" s="6" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="J227" s="6" t="inlineStr">
-        <is>
-          <t>Trivia</t>
-        </is>
-      </c>
-      <c r="K227" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/midiacom/Ereberus-robot/blob/master/Ereberus-robot-uff-source-code/Ereberus-software-uff/db.json</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t>Atrás</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" s="8">
-      <c r="A228" s="6" t="n">
-        <v>238</v>
-      </c>
-      <c r="B228" s="6" t="inlineStr">
-        <is>
-          <t>Preguntas y Respuestas</t>
-        </is>
-      </c>
-      <c r="C228" s="6" t="n">
-        <v>134</v>
-      </c>
-      <c r="D228" s="6" t="inlineStr">
-        <is>
-          <t>Pregunta de contenido</t>
-        </is>
-      </c>
-      <c r="E228" s="6" t="inlineStr">
-        <is>
-          <t>¿Qué tipo de animal es la ballena?</t>
-        </is>
-      </c>
-      <c r="F228" s="6" t="inlineStr">
-        <is>
-          <t>Mamífero marino</t>
-        </is>
-      </c>
-      <c r="G228" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="H228" s="6" t="inlineStr">
-        <is>
-          <t>Trivia / conocimiento</t>
-        </is>
-      </c>
-      <c r="I228" s="6" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="J228" s="6" t="inlineStr">
-        <is>
-          <t>Trivia</t>
-        </is>
-      </c>
-      <c r="K228" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/midiacom/Ereberus-robot/blob/master/Ereberus-robot-uff-source-code/Ereberus-software-uff/db.json</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="O228" t="inlineStr">
-        <is>
           <t>Izquierda</t>
         </is>
       </c>
     </row>
-    <row r="229" s="8">
-      <c r="A229" s="6" t="n">
-        <v>239</v>
-      </c>
-      <c r="B229" s="6" t="inlineStr">
-        <is>
-          <t>Preguntas y Respuestas</t>
-        </is>
-      </c>
-      <c r="C229" s="6" t="n">
-        <v>135</v>
-      </c>
-      <c r="D229" s="6" t="inlineStr">
-        <is>
-          <t>Pregunta de contenido</t>
-        </is>
-      </c>
-      <c r="E229" s="6" t="inlineStr">
-        <is>
-          <t>¿Qué veterano músico es la canción Tears in Heaven?</t>
-        </is>
-      </c>
-      <c r="F229" s="6" t="inlineStr">
-        <is>
-          <t>Eric Clapton</t>
-        </is>
-      </c>
-      <c r="G229" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="H229" s="6" t="inlineStr">
-        <is>
-          <t>Trivia / conocimiento</t>
-        </is>
-      </c>
-      <c r="I229" s="6" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="J229" s="6" t="inlineStr">
-        <is>
-          <t>Trivia</t>
-        </is>
-      </c>
-      <c r="K229" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/midiacom/Ereberus-robot/blob/master/Ereberus-robot-uff-source-code/Ereberus-software-uff/db.json</t>
-        </is>
-      </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>Derecha</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" s="8">
-      <c r="A230" t="n">
-        <v>247</v>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Interacción: música agregada a mano</t>
-        </is>
-      </c>
-      <c r="C230" t="n">
-        <v>1</v>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>Interacción — Pregunta</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>Te voy a poner una canción, ¿sabes cómo se llama?</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>Danza Kuduro</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Feliz / Neutral / Triste</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Socialización / conversación</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>Reconocimiento Musical</t>
-        </is>
-      </c>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t>Feliz</t>
-        </is>
-      </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>Triste</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>danza-kuduro.mp3</t>
-        </is>
-      </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>Atrás</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" s="8">
-      <c r="A231" t="n">
-        <v>248</v>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Interacción: música agregada a mano</t>
-        </is>
-      </c>
-      <c r="C231" t="n">
-        <v>1</v>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Interacción — Pregunta</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Escuchá esto, ¿qué canción es?</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>More Than Words</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Feliz / Neutral / Triste</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Socialización / conversación</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>Reconocimiento Musical</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>Feliz</t>
-        </is>
-      </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>Triste</t>
-        </is>
-      </c>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>more-than-words-heaven.mp3</t>
-        </is>
-      </c>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>Izquierda</t>
-        </is>
-      </c>
-    </row>
+    <row r="227" s="8"/>
+    <row r="228" s="8"/>
+    <row r="229" s="8"/>
+    <row r="230" s="8"/>
+    <row r="231" s="8"/>
     <row r="232" s="8"/>
     <row r="233" s="8"/>
     <row r="234" s="8"/>
